--- a/MRB库存.xlsx
+++ b/MRB库存.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="511">
   <si>
     <t>物料编码</t>
   </si>
@@ -226,15 +226,6 @@
     <t>M12x50-GBT70.1-01</t>
   </si>
   <si>
-    <t>02.04.00300</t>
-  </si>
-  <si>
-    <t>插头上壳</t>
-  </si>
-  <si>
-    <t>CS05-02,V1.2</t>
-  </si>
-  <si>
     <t>02.07.00335</t>
   </si>
   <si>
@@ -247,6 +238,18 @@
     <t>M4x16-GBT70.1-T01</t>
   </si>
   <si>
+    <t>04.24.00020</t>
+  </si>
+  <si>
+    <t>WIFI模块</t>
+  </si>
+  <si>
+    <t>Lantronix_XPC240300B-02</t>
+  </si>
+  <si>
+    <t>射频类IC</t>
+  </si>
+  <si>
     <t>02.04.00232</t>
   </si>
   <si>
@@ -361,6 +364,18 @@
     <t>NJ140101-17-05,V1.0</t>
   </si>
   <si>
+    <t>02.01.00596</t>
+  </si>
+  <si>
+    <t>平皮带</t>
+  </si>
+  <si>
+    <t>P2-20mm宽-1555mm长（平皮带进口-白色）</t>
+  </si>
+  <si>
+    <t>标准件</t>
+  </si>
+  <si>
     <t>04.09.01966</t>
   </si>
   <si>
@@ -412,15 +427,6 @@
     <t>RS8DA02-AN-01,V1.0</t>
   </si>
   <si>
-    <t>02.03.02785</t>
-  </si>
-  <si>
-    <t>平皮带轮</t>
-  </si>
-  <si>
-    <t>RS8DA02-TW-04-06-01,V1.0</t>
-  </si>
-  <si>
     <t>10.03.00053</t>
   </si>
   <si>
@@ -463,7 +469,13 @@
     <t>SK8</t>
   </si>
   <si>
-    <t>标准件</t>
+    <t>02.01.00612</t>
+  </si>
+  <si>
+    <t>直线轴承</t>
+  </si>
+  <si>
+    <t>LMK8LUU</t>
   </si>
   <si>
     <t>04.09.02281</t>
@@ -475,15 +487,6 @@
     <t>W25CH-V1.1</t>
   </si>
   <si>
-    <t>10.01.00123</t>
-  </si>
-  <si>
-    <t>MainControlBoard_A8-三防</t>
-  </si>
-  <si>
-    <t>,MainControlBoard_A8-三防</t>
-  </si>
-  <si>
     <t>04.02.00054</t>
   </si>
   <si>
@@ -733,12 +736,6 @@
     <t>P40R20-JS-00,V1.2</t>
   </si>
   <si>
-    <t>10.12.00240</t>
-  </si>
-  <si>
-    <t>MTC-01(A4.4)-C</t>
-  </si>
-  <si>
     <t>10.12.00241</t>
   </si>
   <si>
@@ -763,6 +760,15 @@
     <t>欧镭_LR-1F-JZJ</t>
   </si>
   <si>
+    <t>10.12.00245</t>
+  </si>
+  <si>
+    <t>接口电路板PCBA-三防</t>
+  </si>
+  <si>
+    <t>INF-11(A1.0)-C</t>
+  </si>
+  <si>
     <t>02.05.04600</t>
   </si>
   <si>
@@ -964,15 +970,6 @@
     <t>RS11DX01-WK-01,V1.0</t>
   </si>
   <si>
-    <t>02.04.01317</t>
-  </si>
-  <si>
-    <t>伸缩叉底部缓冲块</t>
-  </si>
-  <si>
-    <t>RS8DX01-SJ-02-01-01-05,V1.0</t>
-  </si>
-  <si>
     <t>18.28.00639</t>
   </si>
   <si>
@@ -991,6 +988,18 @@
     <t>兰宝_PDB-CC50DGR 1001</t>
   </si>
   <si>
+    <t>17.01.03490</t>
+  </si>
+  <si>
+    <t>取货机构右侧框架</t>
+  </si>
+  <si>
+    <t>NJ140114-09-01,V1.0</t>
+  </si>
+  <si>
+    <t>机加件（钣金、焊接）</t>
+  </si>
+  <si>
     <t>02.03.03982</t>
   </si>
   <si>
@@ -1120,13 +1129,13 @@
     <t>RS8T-WNT-DP-17-03,V1.1</t>
   </si>
   <si>
-    <t>03.02.00116</t>
-  </si>
-  <si>
-    <t>动力锂离子电池包</t>
-  </si>
-  <si>
-    <t>博力威_GKB5030-A07N-SV</t>
+    <t>02.07.01330</t>
+  </si>
+  <si>
+    <t>全金属六角法兰面锁紧螺母</t>
+  </si>
+  <si>
+    <t>M5-GBT6187-01,V1.0</t>
   </si>
   <si>
     <t>02.03.04121</t>
@@ -1153,15 +1162,6 @@
     <t>M5x6-GBT70.2-02,V1.0</t>
   </si>
   <si>
-    <t>15.05.00003</t>
-  </si>
-  <si>
-    <t>GU-INF-002 V00.00</t>
-  </si>
-  <si>
-    <t>接口组件</t>
-  </si>
-  <si>
     <t>02.03.04221</t>
   </si>
   <si>
@@ -1189,6 +1189,15 @@
     <t>RS11DX40-SJ-02-01-32,V1.0</t>
   </si>
   <si>
+    <t>02.03.04202</t>
+  </si>
+  <si>
+    <t>灯带透光板</t>
+  </si>
+  <si>
+    <t>RS11DX40-SJ-02-06,V1.0</t>
+  </si>
+  <si>
     <t>02.04.01416</t>
   </si>
   <si>
@@ -1246,15 +1255,6 @@
     <t>GM-H110A0-13C25C4-S1B1G10-A0</t>
   </si>
   <si>
-    <t>15.10.00018</t>
-  </si>
-  <si>
-    <t>行走电机组件抱闸版</t>
-  </si>
-  <si>
-    <t>GM-H110A0-15C25C4-M1B1G10-G0</t>
-  </si>
-  <si>
     <t>17.02.03752</t>
   </si>
   <si>
@@ -1297,6 +1297,12 @@
     <t>W186CON-V1.0</t>
   </si>
   <si>
+    <t>04.09.02818</t>
+  </si>
+  <si>
+    <t>W322MC-V1.2</t>
+  </si>
+  <si>
     <t>10.13.00204</t>
   </si>
   <si>
@@ -1315,15 +1321,6 @@
     <t>MP10R12-XZ-02,V1.1</t>
   </si>
   <si>
-    <t>04.03.00288</t>
-  </si>
-  <si>
-    <t>PNP型漫反射传感器</t>
-  </si>
-  <si>
-    <t>SUENW_EW-BGD300PO-01</t>
-  </si>
-  <si>
     <t>04.09.02860</t>
   </si>
   <si>
@@ -1351,9 +1348,6 @@
     <t>NJ140125-01-07,V1.0</t>
   </si>
   <si>
-    <t>机加件（钣金、焊接）</t>
-  </si>
-  <si>
     <t>02.03.04414</t>
   </si>
   <si>
@@ -1441,15 +1435,6 @@
     <t>X12H01-JS-01-05,V1.0</t>
   </si>
   <si>
-    <t>02.03.04485</t>
-  </si>
-  <si>
-    <t>轴套</t>
-  </si>
-  <si>
-    <t>X12H01-JS-13,V1.1</t>
-  </si>
-  <si>
     <t>04.03.00297</t>
   </si>
   <si>
@@ -1486,6 +1471,15 @@
     <t>GU-MC-001 V02.05</t>
   </si>
   <si>
+    <t>04.09.02944</t>
+  </si>
+  <si>
+    <t>取箱机构集成线束</t>
+  </si>
+  <si>
+    <t>W82SUB-V1.3</t>
+  </si>
+  <si>
     <t>02.05.05541</t>
   </si>
   <si>
@@ -1517,6 +1511,15 @@
   </si>
   <si>
     <t>RS11DA40-TW-01-03,v1.0</t>
+  </si>
+  <si>
+    <t>02.03.04852</t>
+  </si>
+  <si>
+    <t>移动座右</t>
+  </si>
+  <si>
+    <t>RS11DA40-TW-04-11,V1.1</t>
   </si>
   <si>
     <t>02.05.05621</t>
@@ -3029,11 +3032,9 @@
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="2">
-        <v>1</v>
-      </c>
+      <c r="O5" s="1"/>
       <c r="P5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -3395,16 +3396,16 @@
         <v>64</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>23</v>
@@ -3423,26 +3424,26 @@
         <v>27</v>
       </c>
       <c r="L14" s="2">
-        <v>1</v>
-      </c>
-      <c r="M14" s="2">
-        <v>1</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+      <c r="R14" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>21</v>
@@ -3467,23 +3468,25 @@
         <v>27</v>
       </c>
       <c r="L15" s="2">
-        <v>32</v>
+        <v>2249</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
+      <c r="Q15" s="2">
+        <v>2239</v>
+      </c>
       <c r="R15" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>70</v>
@@ -3492,7 +3495,7 @@
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>23</v>
@@ -3511,28 +3514,26 @@
         <v>27</v>
       </c>
       <c r="L16" s="2">
-        <v>2249</v>
-      </c>
-      <c r="M16" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="2">
-        <v>2239</v>
-      </c>
-      <c r="R16" s="2">
-        <v>10</v>
-      </c>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
@@ -3570,13 +3571,13 @@
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>21</v>
@@ -3614,13 +3615,13 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>21</v>
@@ -3658,13 +3659,13 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>21</v>
@@ -3704,22 +3705,22 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>24</v>
@@ -3748,13 +3749,13 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>21</v>
@@ -3792,19 +3793,19 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>23</v>
@@ -3820,7 +3821,7 @@
         <v>26</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L23" s="2">
         <v>35</v>
@@ -3836,22 +3837,22 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>24</v>
@@ -3880,13 +3881,13 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>21</v>
@@ -3924,19 +3925,19 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>23</v>
@@ -3968,22 +3969,22 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>24</v>
@@ -4012,19 +4013,19 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>23</v>
@@ -4040,7 +4041,7 @@
         <v>26</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L28" s="2">
         <v>1</v>
@@ -4056,19 +4057,19 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>23</v>
@@ -4087,26 +4088,26 @@
         <v>27</v>
       </c>
       <c r="L29" s="2">
-        <v>2</v>
-      </c>
-      <c r="M29" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="M29" s="2">
+        <v>120</v>
+      </c>
       <c r="N29" s="1"/>
-      <c r="O29" s="2">
-        <v>2</v>
-      </c>
+      <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>21</v>
@@ -4131,34 +4132,32 @@
         <v>27</v>
       </c>
       <c r="L30" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="2">
-        <v>3</v>
-      </c>
-      <c r="P30" s="2">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>23</v>
@@ -4177,35 +4176,37 @@
         <v>27</v>
       </c>
       <c r="L31" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="O31" s="2">
+        <v>3</v>
+      </c>
       <c r="P31" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>24</v>
@@ -4234,22 +4235,22 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>24</v>
@@ -4267,30 +4268,30 @@
       <c r="L33" s="2">
         <v>1</v>
       </c>
-      <c r="M33" s="2">
-        <v>1</v>
-      </c>
+      <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
+      <c r="P33" s="2">
+        <v>1</v>
+      </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>23</v>
@@ -4311,33 +4312,33 @@
       <c r="L34" s="2">
         <v>1</v>
       </c>
-      <c r="M34" s="1"/>
+      <c r="M34" s="2">
+        <v>1</v>
+      </c>
       <c r="N34" s="1"/>
-      <c r="O34" s="2">
-        <v>1</v>
-      </c>
+      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>24</v>
@@ -4366,13 +4367,13 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>21</v>
@@ -4410,19 +4411,19 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>23</v>
@@ -4454,19 +4455,19 @@
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -4498,19 +4499,19 @@
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>23</v>
@@ -4542,22 +4543,22 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>24</v>
@@ -4586,19 +4587,19 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>23</v>
@@ -4630,19 +4631,19 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>23</v>
@@ -4674,19 +4675,19 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>23</v>
@@ -4718,22 +4719,22 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>24</v>
@@ -4762,13 +4763,13 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>21</v>
@@ -4806,22 +4807,22 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>24</v>
@@ -4843,10 +4844,10 @@
       <c r="N46" s="2">
         <v>2</v>
       </c>
-      <c r="O46" s="2">
+      <c r="O46" s="1"/>
+      <c r="P46" s="2">
         <v>2</v>
       </c>
-      <c r="P46" s="1"/>
       <c r="Q46" s="2">
         <v>1</v>
       </c>
@@ -4854,13 +4855,13 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>21</v>
@@ -4898,13 +4899,13 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>21</v>
@@ -4942,13 +4943,13 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>21</v>
@@ -4986,13 +4987,13 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>21</v>
@@ -5030,13 +5031,13 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>21</v>
@@ -5074,19 +5075,19 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>23</v>
@@ -5120,13 +5121,13 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>21</v>
@@ -5164,13 +5165,13 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>21</v>
@@ -5208,19 +5209,19 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>23</v>
@@ -5252,19 +5253,19 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -5298,13 +5299,13 @@
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>21</v>
@@ -5342,19 +5343,19 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>23</v>
@@ -5386,19 +5387,19 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>23</v>
@@ -5430,13 +5431,13 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>21</v>
@@ -5474,22 +5475,22 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>24</v>
@@ -5511,22 +5512,22 @@
       <c r="N61" s="2">
         <v>2</v>
       </c>
-      <c r="O61" s="2">
-        <v>1</v>
-      </c>
-      <c r="P61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="2">
+        <v>1</v>
+      </c>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>21</v>
@@ -5564,19 +5565,19 @@
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>23</v>
@@ -5610,19 +5611,19 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>23</v>
@@ -5656,19 +5657,19 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>23</v>
@@ -5700,22 +5701,22 @@
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>24</v>
@@ -5744,22 +5745,22 @@
     </row>
     <row r="67" spans="1:18">
       <c r="A67" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>24</v>
@@ -5788,22 +5789,22 @@
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>24</v>
@@ -5819,10 +5820,10 @@
         <v>27</v>
       </c>
       <c r="L68" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
@@ -5832,22 +5833,22 @@
     </row>
     <row r="69" spans="1:18">
       <c r="A69" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>95</v>
+        <v>235</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>24</v>
@@ -5863,35 +5864,35 @@
         <v>27</v>
       </c>
       <c r="L69" s="2">
-        <v>1</v>
-      </c>
-      <c r="M69" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
+      <c r="P69" s="2">
+        <v>2</v>
+      </c>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
     </row>
     <row r="70" spans="1:18">
       <c r="A70" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>24</v>
@@ -5907,32 +5908,32 @@
         <v>27</v>
       </c>
       <c r="L70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
+      <c r="N70" s="2">
+        <v>1</v>
+      </c>
       <c r="O70" s="1"/>
-      <c r="P70" s="2">
-        <v>2</v>
-      </c>
+      <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>23</v>
@@ -5964,22 +5965,22 @@
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>24</v>
@@ -5997,10 +5998,10 @@
       <c r="L72" s="2">
         <v>1</v>
       </c>
-      <c r="M72" s="1"/>
-      <c r="N72" s="2">
-        <v>1</v>
-      </c>
+      <c r="M72" s="2">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1"/>
       <c r="O72" s="1"/>
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
@@ -6008,19 +6009,19 @@
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -6052,19 +6053,19 @@
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>23</v>
@@ -6098,19 +6099,19 @@
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>23</v>
@@ -6146,19 +6147,19 @@
     </row>
     <row r="76" spans="1:18">
       <c r="A76" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>23</v>
@@ -6190,13 +6191,13 @@
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>21</v>
@@ -6234,19 +6235,19 @@
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>23</v>
@@ -6267,10 +6268,10 @@
       <c r="L78" s="2">
         <v>1</v>
       </c>
-      <c r="M78" s="2">
-        <v>1</v>
-      </c>
-      <c r="N78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="2">
+        <v>1</v>
+      </c>
       <c r="O78" s="1"/>
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
@@ -6278,13 +6279,13 @@
     </row>
     <row r="79" spans="1:18">
       <c r="A79" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>21</v>
@@ -6322,22 +6323,22 @@
     </row>
     <row r="80" spans="1:18">
       <c r="A80" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>24</v>
@@ -6370,13 +6371,13 @@
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>21</v>
@@ -6414,13 +6415,13 @@
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>21</v>
@@ -6458,19 +6459,19 @@
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>23</v>
@@ -6502,13 +6503,13 @@
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>21</v>
@@ -6535,10 +6536,10 @@
       <c r="L84" s="2">
         <v>1</v>
       </c>
-      <c r="M84" s="2">
-        <v>1</v>
-      </c>
-      <c r="N84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="2">
+        <v>1</v>
+      </c>
       <c r="O84" s="1"/>
       <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
@@ -6546,13 +6547,13 @@
     </row>
     <row r="85" spans="1:18">
       <c r="A85" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>21</v>
@@ -6590,13 +6591,13 @@
     </row>
     <row r="86" spans="1:18">
       <c r="A86" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>21</v>
@@ -6634,19 +6635,19 @@
     </row>
     <row r="87" spans="1:18">
       <c r="A87" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -6678,19 +6679,19 @@
     </row>
     <row r="88" spans="1:18">
       <c r="A88" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>23</v>
@@ -6722,22 +6723,22 @@
     </row>
     <row r="89" spans="1:18">
       <c r="A89" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>24</v>
@@ -6766,13 +6767,13 @@
     </row>
     <row r="90" spans="1:18">
       <c r="A90" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>21</v>
@@ -6810,13 +6811,13 @@
     </row>
     <row r="91" spans="1:18">
       <c r="A91" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>21</v>
@@ -6854,13 +6855,13 @@
     </row>
     <row r="92" spans="1:18">
       <c r="A92" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>21</v>
@@ -6888,9 +6889,11 @@
         <v>2</v>
       </c>
       <c r="M92" s="2">
-        <v>2</v>
-      </c>
-      <c r="N92" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="N92" s="2">
+        <v>1</v>
+      </c>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -6898,13 +6901,13 @@
     </row>
     <row r="93" spans="1:18">
       <c r="A93" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>21</v>
@@ -6942,19 +6945,19 @@
     </row>
     <row r="94" spans="1:18">
       <c r="A94" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -6986,19 +6989,19 @@
     </row>
     <row r="95" spans="1:18">
       <c r="A95" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>22</v>
+        <v>209</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -7030,19 +7033,19 @@
     </row>
     <row r="96" spans="1:18">
       <c r="A96" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -7061,10 +7064,10 @@
         <v>27</v>
       </c>
       <c r="L96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
@@ -7074,13 +7077,13 @@
     </row>
     <row r="97" spans="1:18">
       <c r="A97" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>21</v>
@@ -7120,19 +7123,19 @@
     </row>
     <row r="98" spans="1:18">
       <c r="A98" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -7142,7 +7145,7 @@
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>26</v>
@@ -7164,19 +7167,19 @@
     </row>
     <row r="99" spans="1:18">
       <c r="A99" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -7198,23 +7201,23 @@
         <v>10</v>
       </c>
       <c r="M99" s="1"/>
-      <c r="N99" s="2">
+      <c r="N99" s="1"/>
+      <c r="O99" s="2">
         <v>10</v>
       </c>
-      <c r="O99" s="1"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
     <row r="100" spans="1:18">
       <c r="A100" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>21</v>
@@ -7254,19 +7257,19 @@
     </row>
     <row r="101" spans="1:18">
       <c r="A101" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>23</v>
@@ -7298,19 +7301,19 @@
     </row>
     <row r="102" spans="1:18">
       <c r="A102" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>23</v>
@@ -7342,13 +7345,13 @@
     </row>
     <row r="103" spans="1:18">
       <c r="A103" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>21</v>
@@ -7386,22 +7389,22 @@
     </row>
     <row r="104" spans="1:18">
       <c r="A104" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>24</v>
@@ -7430,13 +7433,13 @@
     </row>
     <row r="105" spans="1:18">
       <c r="A105" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>21</v>
@@ -7474,13 +7477,13 @@
     </row>
     <row r="106" spans="1:18">
       <c r="A106" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>21</v>
@@ -7518,22 +7521,22 @@
     </row>
     <row r="107" spans="1:18">
       <c r="A107" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>24</v>
@@ -7562,19 +7565,19 @@
     </row>
     <row r="108" spans="1:18">
       <c r="A108" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>23</v>
@@ -7606,13 +7609,13 @@
     </row>
     <row r="109" spans="1:18">
       <c r="A109" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>21</v>
@@ -7650,19 +7653,19 @@
     </row>
     <row r="110" spans="1:18">
       <c r="A110" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>23</v>
@@ -7694,19 +7697,19 @@
     </row>
     <row r="111" spans="1:18">
       <c r="A111" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>23</v>
@@ -7725,10 +7728,10 @@
         <v>27</v>
       </c>
       <c r="L111" s="2">
-        <v>8</v>
+        <v>1810</v>
       </c>
       <c r="M111" s="2">
-        <v>8</v>
+        <v>1810</v>
       </c>
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
@@ -7738,13 +7741,13 @@
     </row>
     <row r="112" spans="1:18">
       <c r="A112" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>21</v>
@@ -7782,13 +7785,13 @@
     </row>
     <row r="113" spans="1:18">
       <c r="A113" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>21</v>
@@ -7826,13 +7829,13 @@
     </row>
     <row r="114" spans="1:18">
       <c r="A114" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>21</v>
@@ -7870,22 +7873,22 @@
     </row>
     <row r="115" spans="1:18">
       <c r="A115" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>130</v>
+        <v>377</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>375</v>
+        <v>55</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>24</v>
@@ -7901,12 +7904,14 @@
         <v>27</v>
       </c>
       <c r="L115" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M115" s="2">
         <v>1</v>
       </c>
-      <c r="N115" s="1"/>
+      <c r="N115" s="2">
+        <v>1</v>
+      </c>
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
@@ -7914,13 +7919,13 @@
     </row>
     <row r="116" spans="1:18">
       <c r="A116" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>21</v>
@@ -7945,10 +7950,10 @@
         <v>27</v>
       </c>
       <c r="L116" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="M116" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
@@ -7958,13 +7963,13 @@
     </row>
     <row r="117" spans="1:18">
       <c r="A117" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>21</v>
@@ -7989,12 +7994,12 @@
         <v>27</v>
       </c>
       <c r="L117" s="2">
-        <v>53</v>
-      </c>
-      <c r="M117" s="2">
-        <v>53</v>
-      </c>
-      <c r="N117" s="1"/>
+        <v>485</v>
+      </c>
+      <c r="M117" s="1"/>
+      <c r="N117" s="2">
+        <v>485</v>
+      </c>
       <c r="O117" s="1"/>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
@@ -8002,13 +8007,13 @@
     </row>
     <row r="118" spans="1:18">
       <c r="A118" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>21</v>
@@ -8033,10 +8038,10 @@
         <v>27</v>
       </c>
       <c r="L118" s="2">
-        <v>711</v>
+        <v>6</v>
       </c>
       <c r="M118" s="2">
-        <v>711</v>
+        <v>6</v>
       </c>
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
@@ -8046,13 +8051,13 @@
     </row>
     <row r="119" spans="1:18">
       <c r="A119" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>21</v>
@@ -8092,13 +8097,13 @@
     </row>
     <row r="120" spans="1:18">
       <c r="A120" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>21</v>
@@ -8136,19 +8141,19 @@
     </row>
     <row r="121" spans="1:18">
       <c r="A121" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -8180,13 +8185,13 @@
     </row>
     <row r="122" spans="1:18">
       <c r="A122" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>21</v>
@@ -8224,19 +8229,19 @@
     </row>
     <row r="123" spans="1:18">
       <c r="A123" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>23</v>
@@ -8268,22 +8273,22 @@
     </row>
     <row r="124" spans="1:18">
       <c r="A124" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>24</v>
@@ -8312,22 +8317,22 @@
     </row>
     <row r="125" spans="1:18">
       <c r="A125" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>24</v>
@@ -8356,22 +8361,22 @@
     </row>
     <row r="126" spans="1:18">
       <c r="A126" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>164</v>
+        <v>410</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>24</v>
@@ -8387,32 +8392,32 @@
         <v>27</v>
       </c>
       <c r="L126" s="2">
-        <v>2</v>
-      </c>
-      <c r="M126" s="2">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M126" s="1"/>
       <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
+      <c r="O126" s="2">
+        <v>1</v>
+      </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
     </row>
     <row r="127" spans="1:18">
       <c r="A127" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>23</v>
@@ -8431,32 +8436,32 @@
         <v>27</v>
       </c>
       <c r="L127" s="2">
-        <v>1</v>
-      </c>
-      <c r="M127" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="M127" s="2">
+        <v>40</v>
+      </c>
       <c r="N127" s="1"/>
-      <c r="O127" s="2">
-        <v>1</v>
-      </c>
+      <c r="O127" s="1"/>
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
     </row>
     <row r="128" spans="1:18">
       <c r="A128" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>414</v>
+        <v>22</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -8475,10 +8480,10 @@
         <v>27</v>
       </c>
       <c r="L128" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
@@ -8488,13 +8493,13 @@
     </row>
     <row r="129" spans="1:18">
       <c r="A129" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>21</v>
@@ -8519,26 +8524,26 @@
         <v>27</v>
       </c>
       <c r="L129" s="2">
-        <v>2</v>
-      </c>
-      <c r="M129" s="2">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M129" s="1"/>
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
-      <c r="R129" s="1"/>
+      <c r="R129" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" spans="1:18">
       <c r="A130" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>419</v>
+        <v>286</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>21</v>
@@ -8565,33 +8570,33 @@
       <c r="L130" s="2">
         <v>1</v>
       </c>
-      <c r="M130" s="1"/>
+      <c r="M130" s="2">
+        <v>1</v>
+      </c>
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
-      <c r="R130" s="2">
-        <v>1</v>
-      </c>
+      <c r="R130" s="1"/>
     </row>
     <row r="131" spans="1:18">
       <c r="A131" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>24</v>
@@ -8620,13 +8625,13 @@
     </row>
     <row r="132" spans="1:18">
       <c r="A132" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>21</v>
@@ -8664,19 +8669,19 @@
     </row>
     <row r="133" spans="1:18">
       <c r="A133" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -8708,22 +8713,22 @@
     </row>
     <row r="134" spans="1:18">
       <c r="A134" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>24</v>
@@ -8741,33 +8746,33 @@
       <c r="L134" s="2">
         <v>1</v>
       </c>
-      <c r="M134" s="2">
-        <v>1</v>
-      </c>
+      <c r="M134" s="1"/>
       <c r="N134" s="1"/>
-      <c r="O134" s="1"/>
+      <c r="O134" s="2">
+        <v>1</v>
+      </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
     <row r="135" spans="1:18">
       <c r="A135" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>97</v>
+        <v>321</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>24</v>
@@ -8785,30 +8790,30 @@
       <c r="L135" s="2">
         <v>1</v>
       </c>
-      <c r="M135" s="1"/>
+      <c r="M135" s="2">
+        <v>1</v>
+      </c>
       <c r="N135" s="1"/>
-      <c r="O135" s="2">
-        <v>1</v>
-      </c>
+      <c r="O135" s="1"/>
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
     </row>
     <row r="136" spans="1:18">
       <c r="A136" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>439</v>
+        <v>55</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>23</v>
@@ -8829,30 +8834,30 @@
       <c r="L136" s="2">
         <v>1</v>
       </c>
-      <c r="M136" s="2">
-        <v>1</v>
-      </c>
+      <c r="M136" s="1"/>
       <c r="N136" s="1"/>
-      <c r="O136" s="1"/>
+      <c r="O136" s="2">
+        <v>1</v>
+      </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
     </row>
     <row r="137" spans="1:18">
       <c r="A137" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>23</v>
@@ -8873,33 +8878,33 @@
       <c r="L137" s="2">
         <v>1</v>
       </c>
-      <c r="M137" s="1"/>
+      <c r="M137" s="2">
+        <v>1</v>
+      </c>
       <c r="N137" s="1"/>
-      <c r="O137" s="2">
-        <v>1</v>
-      </c>
+      <c r="O137" s="1"/>
       <c r="P137" s="1"/>
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
     </row>
     <row r="138" spans="1:18">
       <c r="A138" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>444</v>
+        <v>134</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>445</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>118</v>
+        <v>446</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>24</v>
@@ -8915,12 +8920,14 @@
         <v>27</v>
       </c>
       <c r="L138" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M138" s="2">
-        <v>1</v>
-      </c>
-      <c r="N138" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="N138" s="2">
+        <v>3</v>
+      </c>
       <c r="O138" s="1"/>
       <c r="P138" s="1"/>
       <c r="Q138" s="1"/>
@@ -8928,22 +8935,22 @@
     </row>
     <row r="139" spans="1:18">
       <c r="A139" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>132</v>
+        <v>448</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>448</v>
+        <v>141</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>24</v>
@@ -8959,37 +8966,35 @@
         <v>27</v>
       </c>
       <c r="L139" s="2">
-        <v>5</v>
-      </c>
-      <c r="M139" s="2">
-        <v>2</v>
-      </c>
-      <c r="N139" s="2">
         <v>3</v>
       </c>
-      <c r="O139" s="1"/>
+      <c r="M139" s="1"/>
+      <c r="N139" s="1"/>
+      <c r="O139" s="2">
+        <v>3</v>
+      </c>
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
     </row>
     <row r="140" spans="1:18">
       <c r="A140" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>139</v>
+        <v>299</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>24</v>
@@ -9005,12 +9010,12 @@
         <v>27</v>
       </c>
       <c r="L140" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
       <c r="O140" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1"/>
@@ -9018,22 +9023,22 @@
     </row>
     <row r="141" spans="1:18">
       <c r="A141" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>297</v>
+        <v>141</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>24</v>
@@ -9062,19 +9067,19 @@
     </row>
     <row r="142" spans="1:18">
       <c r="A142" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>23</v>
@@ -9106,22 +9111,22 @@
     </row>
     <row r="143" spans="1:18">
       <c r="A143" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>459</v>
+        <v>134</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>460</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>22</v>
+        <v>446</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>24</v>
@@ -9137,13 +9142,15 @@
         <v>27</v>
       </c>
       <c r="L143" s="2">
-        <v>1</v>
-      </c>
-      <c r="M143" s="1"/>
-      <c r="N143" s="1"/>
-      <c r="O143" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M143" s="2">
+        <v>1</v>
+      </c>
+      <c r="N143" s="2">
+        <v>1</v>
+      </c>
+      <c r="O143" s="1"/>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
@@ -9153,19 +9160,19 @@
         <v>461</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>132</v>
+        <v>462</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>448</v>
+        <v>55</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>24</v>
@@ -9181,28 +9188,26 @@
         <v>27</v>
       </c>
       <c r="L144" s="2">
-        <v>2</v>
-      </c>
-      <c r="M144" s="2">
-        <v>1</v>
-      </c>
-      <c r="N144" s="2">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M144" s="1"/>
+      <c r="N144" s="1"/>
       <c r="O144" s="1"/>
-      <c r="P144" s="1"/>
+      <c r="P144" s="2">
+        <v>1</v>
+      </c>
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
     </row>
     <row r="145" spans="1:18">
       <c r="A145" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>21</v>
@@ -9240,10 +9245,10 @@
     </row>
     <row r="146" spans="1:18">
       <c r="A146" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>467</v>
+        <v>283</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>468</v>
@@ -9252,7 +9257,7 @@
         <v>21</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>23</v>
@@ -9273,12 +9278,12 @@
       <c r="L146" s="2">
         <v>1</v>
       </c>
-      <c r="M146" s="1"/>
+      <c r="M146" s="2">
+        <v>1</v>
+      </c>
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
-      <c r="P146" s="2">
-        <v>1</v>
-      </c>
+      <c r="P146" s="1"/>
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
     </row>
@@ -9296,7 +9301,7 @@
         <v>21</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>23</v>
@@ -9315,11 +9320,11 @@
         <v>27</v>
       </c>
       <c r="L147" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M147" s="1"/>
       <c r="N147" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O147" s="1"/>
       <c r="P147" s="1"/>
@@ -9331,16 +9336,16 @@
         <v>472</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>281</v>
+        <v>473</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>23</v>
@@ -9359,23 +9364,23 @@
         <v>27</v>
       </c>
       <c r="L148" s="2">
-        <v>1</v>
-      </c>
-      <c r="M148" s="2">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M148" s="1"/>
       <c r="N148" s="1"/>
-      <c r="O148" s="1"/>
+      <c r="O148" s="2">
+        <v>4</v>
+      </c>
       <c r="P148" s="1"/>
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
     </row>
     <row r="149" spans="1:18">
       <c r="A149" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>475</v>
+        <v>184</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>476</v>
@@ -9405,10 +9410,10 @@
       <c r="L149" s="2">
         <v>1</v>
       </c>
-      <c r="M149" s="2">
-        <v>1</v>
-      </c>
-      <c r="N149" s="1"/>
+      <c r="M149" s="1"/>
+      <c r="N149" s="2">
+        <v>1</v>
+      </c>
       <c r="O149" s="1"/>
       <c r="P149" s="1"/>
       <c r="Q149" s="1"/>
@@ -9419,19 +9424,19 @@
         <v>477</v>
       </c>
       <c r="B150" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="D150" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>55</v>
+        <v>446</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>24</v>
@@ -9447,23 +9452,23 @@
         <v>27</v>
       </c>
       <c r="L150" s="2">
-        <v>4</v>
-      </c>
-      <c r="M150" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="M150" s="2">
+        <v>3</v>
+      </c>
       <c r="N150" s="1"/>
-      <c r="O150" s="2">
-        <v>4</v>
-      </c>
+      <c r="O150" s="1"/>
       <c r="P150" s="1"/>
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
     </row>
     <row r="151" spans="1:18">
       <c r="A151" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>481</v>
@@ -9472,7 +9477,7 @@
         <v>21</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -9507,19 +9512,19 @@
         <v>482</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>132</v>
+        <v>483</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>448</v>
+        <v>123</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>24</v>
@@ -9535,10 +9540,10 @@
         <v>27</v>
       </c>
       <c r="L152" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
@@ -9548,19 +9553,19 @@
     </row>
     <row r="153" spans="1:18">
       <c r="A153" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -9592,10 +9597,10 @@
     </row>
     <row r="154" spans="1:18">
       <c r="A154" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>488</v>
+        <v>238</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>489</v>
@@ -9604,7 +9609,7 @@
         <v>21</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -9639,16 +9644,16 @@
         <v>490</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>239</v>
+        <v>491</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>23</v>
@@ -9667,10 +9672,10 @@
         <v>27</v>
       </c>
       <c r="L155" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M155" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
@@ -9680,13 +9685,13 @@
     </row>
     <row r="156" spans="1:18">
       <c r="A156" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>21</v>
@@ -9711,10 +9716,10 @@
         <v>27</v>
       </c>
       <c r="L156" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
@@ -9724,19 +9729,19 @@
     </row>
     <row r="157" spans="1:18">
       <c r="A157" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -9787,7 +9792,7 @@
   <sheetData>
     <row r="3" s="3" customFormat="1" spans="1:11">
       <c r="A3" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -9799,170 +9804,170 @@
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
       <c r="K3" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" spans="1:11">
       <c r="A4" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B4" s="10">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="C4" s="10">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="D4" s="10">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E4" s="10">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="F4" s="10">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="G4" s="10">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H4" s="10">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I4" s="10">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K4" s="12">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:11">
       <c r="A5" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B5" s="5">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C5" s="5">
+        <v>89</v>
+      </c>
+      <c r="D5" s="5">
+        <v>33</v>
+      </c>
+      <c r="E5" s="5">
         <v>66</v>
       </c>
-      <c r="D5" s="5">
-        <v>89</v>
-      </c>
-      <c r="E5" s="5">
-        <v>33</v>
-      </c>
       <c r="F5" s="5">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5" s="5">
         <v>68</v>
       </c>
       <c r="H5" s="5">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="5">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J5" s="5">
         <f>I5-H5</f>
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="K5" s="5">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:11">
       <c r="A6" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B6" s="5">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C6" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="5">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="E6" s="5">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="F6" s="5">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G6" s="5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H6" s="5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I6" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J6" s="5">
         <f>I6-H6</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:11">
       <c r="A7" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B7" s="5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C7" s="5">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D7" s="5">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E7" s="5">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F7" s="5">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G7" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H7" s="5">
         <v>28</v>
       </c>
       <c r="I7" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J7" s="5">
         <f>I7-H7</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="K7" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:11">
       <c r="A8" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B8" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D8" s="5">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E8" s="5">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F8" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G8" s="5">
         <v>26</v>
@@ -9971,47 +9976,47 @@
         <v>26</v>
       </c>
       <c r="I8" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J8" s="5">
         <f>I8-H8</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B9" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D9" s="5">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5">
         <v>9</v>
       </c>
       <c r="G9" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" s="5">
         <v>8</v>
       </c>
       <c r="J9" s="5">
         <f>I9-H9</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
         <v>4</v>
@@ -10019,19 +10024,19 @@
     </row>
     <row r="10" s="3" customFormat="1" spans="1:11">
       <c r="A10" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B10" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="5">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D10" s="5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E10" s="5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F10" s="5">
         <v>42</v>
@@ -10040,14 +10045,14 @@
         <v>42</v>
       </c>
       <c r="H10" s="5">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="I10" s="5">
         <v>21</v>
       </c>
       <c r="J10" s="5">
         <f>I10-H10</f>
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5">
         <v>5</v>
@@ -10055,43 +10060,43 @@
     </row>
     <row r="11" s="3" customFormat="1" spans="1:11">
       <c r="A11" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B11" s="5">
         <f t="shared" ref="B11:J11" si="0">SUM(B5:B10)</f>
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C11" s="5">
         <f t="shared" si="0"/>
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="0"/>
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E11" s="5">
         <f t="shared" si="0"/>
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="F11" s="5">
         <f t="shared" si="0"/>
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J11" s="5">
         <f>SUM(J5:J10)</f>
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="K11" s="5">
         <f>SUM(K5:K10)</f>
@@ -10100,7 +10105,7 @@
     </row>
     <row r="14" s="3" customFormat="1" spans="1:11">
       <c r="A14" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -10112,219 +10117,219 @@
       <c r="I14" s="7"/>
       <c r="J14" s="8"/>
       <c r="K14" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" s="4" customFormat="1" spans="1:11">
       <c r="A15" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B15" s="10">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="C15" s="10">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="D15" s="10">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E15" s="10">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="F15" s="10">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="G15" s="10">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H15" s="10">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I15" s="10">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K15" s="12">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:11">
       <c r="A16" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B16" s="5">
-        <v>597</v>
+        <v>349</v>
       </c>
       <c r="C16" s="5">
-        <v>349</v>
+        <v>868</v>
       </c>
       <c r="D16" s="5">
-        <v>868</v>
+        <v>173</v>
       </c>
       <c r="E16" s="5">
-        <v>173</v>
+        <v>1617</v>
       </c>
       <c r="F16" s="5">
-        <v>1617</v>
+        <v>1365</v>
       </c>
       <c r="G16" s="5">
-        <v>1365</v>
+        <v>902</v>
       </c>
       <c r="H16" s="5">
-        <v>902</v>
+        <v>961</v>
       </c>
       <c r="I16" s="5">
-        <v>961</v>
+        <v>2173</v>
       </c>
       <c r="J16" s="5">
         <f>I16-H16</f>
-        <v>59</v>
+        <v>1212</v>
       </c>
       <c r="K16" s="5">
-        <v>961</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B17" s="5">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C17" s="5">
-        <v>381</v>
+        <v>159</v>
       </c>
       <c r="D17" s="5">
-        <v>159</v>
+        <v>2816.9</v>
       </c>
       <c r="E17" s="5">
-        <v>2816.9</v>
+        <v>226</v>
       </c>
       <c r="F17" s="5">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="G17" s="5">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H17" s="5">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I17" s="5">
-        <v>83</v>
+        <v>545</v>
       </c>
       <c r="J17" s="5">
         <f>I17-H17</f>
-        <v>9</v>
+        <v>462</v>
       </c>
       <c r="K17" s="5">
-        <v>83</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:11">
       <c r="A18" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B18" s="5">
-        <v>335</v>
+        <v>571</v>
       </c>
       <c r="C18" s="5">
-        <v>571</v>
+        <v>613</v>
       </c>
       <c r="D18" s="5">
-        <v>613</v>
+        <v>420</v>
       </c>
       <c r="E18" s="5">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="F18" s="5">
-        <v>500</v>
+        <v>346</v>
       </c>
       <c r="G18" s="5">
-        <v>346</v>
+        <v>136</v>
       </c>
       <c r="H18" s="5">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I18" s="5">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J18" s="5">
         <f>I18-H18</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18" s="5">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:11">
       <c r="A19" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B19" s="5">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="C19" s="5">
-        <v>960</v>
+        <v>1125</v>
       </c>
       <c r="D19" s="5">
-        <v>1125</v>
+        <v>551</v>
       </c>
       <c r="E19" s="5">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="F19" s="5">
-        <v>564</v>
+        <v>622</v>
       </c>
       <c r="G19" s="5">
-        <v>622</v>
+        <v>636</v>
       </c>
       <c r="H19" s="5">
-        <v>636</v>
+        <v>475</v>
       </c>
       <c r="I19" s="5">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="J19" s="5">
         <f>I19-H19</f>
-        <v>-161</v>
+        <v>4</v>
       </c>
       <c r="K19" s="5">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:11">
       <c r="A20" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B20" s="5">
-        <v>22577</v>
+        <v>17577</v>
       </c>
       <c r="C20" s="5">
-        <v>17577</v>
+        <v>17231</v>
       </c>
       <c r="D20" s="5">
-        <v>17231</v>
+        <v>6226</v>
       </c>
       <c r="E20" s="5">
-        <v>6226</v>
+        <v>3882</v>
       </c>
       <c r="F20" s="5">
         <v>3882</v>
       </c>
       <c r="G20" s="5">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="H20" s="5">
-        <v>3883</v>
+        <v>3161</v>
       </c>
       <c r="I20" s="5">
         <v>3161</v>
       </c>
       <c r="J20" s="5">
         <f>I20-H20</f>
-        <v>-722</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5">
         <v>58</v>
@@ -10332,19 +10337,19 @@
     </row>
     <row r="21" s="3" customFormat="1" spans="1:11">
       <c r="A21" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B21" s="5">
-        <v>53273</v>
+        <v>58276</v>
       </c>
       <c r="C21" s="5">
-        <v>58276</v>
+        <v>33855</v>
       </c>
       <c r="D21" s="5">
-        <v>33855</v>
+        <v>45575</v>
       </c>
       <c r="E21" s="5">
-        <v>45575</v>
+        <v>38879</v>
       </c>
       <c r="F21" s="5">
         <v>38879</v>
@@ -10353,14 +10358,14 @@
         <v>38879</v>
       </c>
       <c r="H21" s="5">
-        <v>38879</v>
+        <v>5820</v>
       </c>
       <c r="I21" s="5">
         <v>5820</v>
       </c>
       <c r="J21" s="5">
         <f>I21-H21</f>
-        <v>-33059</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5">
         <v>71</v>
@@ -10368,47 +10373,47 @@
     </row>
     <row r="22" s="3" customFormat="1" spans="1:11">
       <c r="A22" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B22" s="5">
         <f t="shared" ref="B22:J22" si="1">SUM(B16:B21)</f>
-        <v>78128</v>
+        <v>78114</v>
       </c>
       <c r="C22" s="5">
         <f t="shared" si="1"/>
-        <v>78114</v>
+        <v>53851</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="1"/>
-        <v>53851</v>
+        <v>55761.9</v>
       </c>
       <c r="E22" s="5">
         <f t="shared" si="1"/>
-        <v>55761.9</v>
+        <v>45668</v>
       </c>
       <c r="F22" s="5">
         <f t="shared" si="1"/>
-        <v>45668</v>
+        <v>45176</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>45176</v>
+        <v>44510</v>
       </c>
       <c r="H22" s="5">
         <f t="shared" si="1"/>
-        <v>44510</v>
+        <v>10635</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="1"/>
-        <v>10635</v>
+        <v>12318</v>
       </c>
       <c r="J22" s="5">
         <f>SUM(J16:J21)</f>
-        <v>-33875</v>
+        <v>1683</v>
       </c>
       <c r="K22" s="5">
         <f>SUM(K16:K21)</f>
-        <v>1407</v>
+        <v>1280</v>
       </c>
     </row>
   </sheetData>
@@ -10424,7 +10429,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R135"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -10608,11 +10613,9 @@
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="2">
-        <v>1</v>
-      </c>
+      <c r="O4" s="1"/>
       <c r="P4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -10751,19 +10754,19 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>23</v>
@@ -10795,13 +10798,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>21</v>
@@ -10839,22 +10842,22 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>24</v>
@@ -10883,13 +10886,13 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>21</v>
@@ -10927,19 +10930,19 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>23</v>
@@ -10955,7 +10958,7 @@
         <v>26</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L12" s="2">
         <v>35</v>
@@ -10971,22 +10974,22 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>24</v>
@@ -11015,19 +11018,19 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>23</v>
@@ -11059,22 +11062,22 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>24</v>
@@ -11103,19 +11106,19 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>23</v>
@@ -11131,7 +11134,7 @@
         <v>26</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L16" s="2">
         <v>1</v>
@@ -11147,19 +11150,19 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>23</v>
@@ -11178,26 +11181,26 @@
         <v>27</v>
       </c>
       <c r="L17" s="2">
-        <v>2</v>
-      </c>
-      <c r="M17" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="M17" s="2">
+        <v>120</v>
+      </c>
       <c r="N17" s="1"/>
-      <c r="O17" s="2">
-        <v>2</v>
-      </c>
+      <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>21</v>
@@ -11222,34 +11225,32 @@
         <v>27</v>
       </c>
       <c r="L18" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="2">
-        <v>3</v>
-      </c>
-      <c r="P18" s="2">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>23</v>
@@ -11268,35 +11269,37 @@
         <v>27</v>
       </c>
       <c r="L19" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="O19" s="2">
+        <v>3</v>
+      </c>
       <c r="P19" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>24</v>
@@ -11325,22 +11328,22 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>24</v>
@@ -11358,30 +11361,30 @@
       <c r="L21" s="2">
         <v>1</v>
       </c>
-      <c r="M21" s="2">
-        <v>1</v>
-      </c>
+      <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
+      <c r="P21" s="2">
+        <v>1</v>
+      </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>23</v>
@@ -11402,33 +11405,33 @@
       <c r="L22" s="2">
         <v>1</v>
       </c>
-      <c r="M22" s="1"/>
+      <c r="M22" s="2">
+        <v>1</v>
+      </c>
       <c r="N22" s="1"/>
-      <c r="O22" s="2">
-        <v>1</v>
-      </c>
+      <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>24</v>
@@ -11457,13 +11460,13 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>21</v>
@@ -11501,19 +11504,19 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>23</v>
@@ -11545,19 +11548,19 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>23</v>
@@ -11589,19 +11592,19 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>23</v>
@@ -11633,22 +11636,22 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>24</v>
@@ -11677,19 +11680,19 @@
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>23</v>
@@ -11721,19 +11724,19 @@
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>23</v>
@@ -11765,19 +11768,19 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>23</v>
@@ -11809,22 +11812,22 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>24</v>
@@ -11853,13 +11856,13 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>21</v>
@@ -11897,22 +11900,22 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>24</v>
@@ -11934,10 +11937,10 @@
       <c r="N34" s="2">
         <v>2</v>
       </c>
-      <c r="O34" s="2">
+      <c r="O34" s="1"/>
+      <c r="P34" s="2">
         <v>2</v>
       </c>
-      <c r="P34" s="1"/>
       <c r="Q34" s="2">
         <v>1</v>
       </c>
@@ -11945,13 +11948,13 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>21</v>
@@ -11989,13 +11992,13 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>21</v>
@@ -12033,13 +12036,13 @@
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>21</v>
@@ -12077,19 +12080,19 @@
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -12123,19 +12126,19 @@
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>23</v>
@@ -12169,19 +12172,19 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>23</v>
@@ -12213,19 +12216,19 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>23</v>
@@ -12257,22 +12260,22 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>24</v>
@@ -12294,28 +12297,28 @@
       <c r="N42" s="2">
         <v>2</v>
       </c>
-      <c r="O42" s="2">
-        <v>1</v>
-      </c>
-      <c r="P42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="2">
+        <v>1</v>
+      </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>23</v>
@@ -12349,19 +12352,19 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>23</v>
@@ -12395,19 +12398,19 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>23</v>
@@ -12439,22 +12442,22 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>24</v>
@@ -12483,22 +12486,22 @@
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>24</v>
@@ -12527,22 +12530,22 @@
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>24</v>
@@ -12558,10 +12561,10 @@
         <v>27</v>
       </c>
       <c r="L48" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -12571,22 +12574,22 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>95</v>
+        <v>235</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>24</v>
@@ -12602,35 +12605,35 @@
         <v>27</v>
       </c>
       <c r="L49" s="2">
-        <v>1</v>
-      </c>
-      <c r="M49" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
+      <c r="P49" s="2">
+        <v>2</v>
+      </c>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>24</v>
@@ -12646,32 +12649,32 @@
         <v>27</v>
       </c>
       <c r="L50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
+      <c r="N50" s="2">
+        <v>1</v>
+      </c>
       <c r="O50" s="1"/>
-      <c r="P50" s="2">
-        <v>2</v>
-      </c>
+      <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>23</v>
@@ -12703,22 +12706,22 @@
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>24</v>
@@ -12736,10 +12739,10 @@
       <c r="L52" s="2">
         <v>1</v>
       </c>
-      <c r="M52" s="1"/>
-      <c r="N52" s="2">
-        <v>1</v>
-      </c>
+      <c r="M52" s="2">
+        <v>1</v>
+      </c>
+      <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
@@ -12747,19 +12750,19 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>23</v>
@@ -12791,19 +12794,19 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>23</v>
@@ -12837,19 +12840,19 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>23</v>
@@ -12885,19 +12888,19 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -12929,19 +12932,19 @@
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>23</v>
@@ -12962,10 +12965,10 @@
       <c r="L57" s="2">
         <v>1</v>
       </c>
-      <c r="M57" s="2">
-        <v>1</v>
-      </c>
-      <c r="N57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="2">
+        <v>1</v>
+      </c>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
@@ -12973,13 +12976,13 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>21</v>
@@ -13017,22 +13020,22 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>24</v>
@@ -13065,13 +13068,13 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>21</v>
@@ -13109,13 +13112,13 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>21</v>
@@ -13153,19 +13156,19 @@
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>23</v>
@@ -13197,13 +13200,13 @@
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>21</v>
@@ -13230,10 +13233,10 @@
       <c r="L63" s="2">
         <v>1</v>
       </c>
-      <c r="M63" s="2">
-        <v>1</v>
-      </c>
-      <c r="N63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="2">
+        <v>1</v>
+      </c>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
@@ -13241,13 +13244,13 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>21</v>
@@ -13285,13 +13288,13 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>21</v>
@@ -13329,19 +13332,19 @@
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>23</v>
@@ -13373,19 +13376,19 @@
     </row>
     <row r="67" spans="1:18">
       <c r="A67" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>23</v>
@@ -13417,22 +13420,22 @@
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>24</v>
@@ -13461,13 +13464,13 @@
     </row>
     <row r="69" spans="1:18">
       <c r="A69" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>21</v>
@@ -13505,13 +13508,13 @@
     </row>
     <row r="70" spans="1:18">
       <c r="A70" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>21</v>
@@ -13549,13 +13552,13 @@
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>21</v>
@@ -13583,9 +13586,11 @@
         <v>2</v>
       </c>
       <c r="M71" s="2">
-        <v>2</v>
-      </c>
-      <c r="N71" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="N71" s="2">
+        <v>1</v>
+      </c>
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
@@ -13593,13 +13598,13 @@
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>21</v>
@@ -13637,19 +13642,19 @@
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>23</v>
@@ -13681,19 +13686,19 @@
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>22</v>
+        <v>209</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>23</v>
@@ -13725,19 +13730,19 @@
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>23</v>
@@ -13756,10 +13761,10 @@
         <v>27</v>
       </c>
       <c r="L75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
@@ -13769,13 +13774,13 @@
     </row>
     <row r="76" spans="1:18">
       <c r="A76" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>21</v>
@@ -13815,19 +13820,19 @@
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>23</v>
@@ -13837,7 +13842,7 @@
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>26</v>
@@ -13859,19 +13864,19 @@
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>23</v>
@@ -13893,23 +13898,23 @@
         <v>10</v>
       </c>
       <c r="M78" s="1"/>
-      <c r="N78" s="2">
+      <c r="N78" s="1"/>
+      <c r="O78" s="2">
         <v>10</v>
       </c>
-      <c r="O78" s="1"/>
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
     </row>
     <row r="79" spans="1:18">
       <c r="A79" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>21</v>
@@ -13949,19 +13954,19 @@
     </row>
     <row r="80" spans="1:18">
       <c r="A80" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>23</v>
@@ -13993,19 +13998,19 @@
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>23</v>
@@ -14037,13 +14042,13 @@
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>21</v>
@@ -14081,22 +14086,22 @@
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>24</v>
@@ -14125,13 +14130,13 @@
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>21</v>
@@ -14169,13 +14174,13 @@
     </row>
     <row r="85" spans="1:18">
       <c r="A85" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>21</v>
@@ -14213,22 +14218,22 @@
     </row>
     <row r="86" spans="1:18">
       <c r="A86" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>24</v>
@@ -14257,19 +14262,19 @@
     </row>
     <row r="87" spans="1:18">
       <c r="A87" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -14301,13 +14306,13 @@
     </row>
     <row r="88" spans="1:18">
       <c r="A88" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>21</v>
@@ -14345,19 +14350,19 @@
     </row>
     <row r="89" spans="1:18">
       <c r="A89" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -14389,19 +14394,19 @@
     </row>
     <row r="90" spans="1:18">
       <c r="A90" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>23</v>
@@ -14420,12 +14425,12 @@
         <v>27</v>
       </c>
       <c r="L90" s="2">
-        <v>8</v>
-      </c>
-      <c r="M90" s="2">
-        <v>8</v>
-      </c>
-      <c r="N90" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="M90" s="1"/>
+      <c r="N90" s="2">
+        <v>1</v>
+      </c>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -14433,13 +14438,13 @@
     </row>
     <row r="91" spans="1:18">
       <c r="A91" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>21</v>
@@ -14477,13 +14482,13 @@
     </row>
     <row r="92" spans="1:18">
       <c r="A92" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>21</v>
@@ -14508,9 +14513,11 @@
         <v>27</v>
       </c>
       <c r="L92" s="2">
-        <v>1</v>
-      </c>
-      <c r="M92" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="M92" s="2">
+        <v>1</v>
+      </c>
       <c r="N92" s="2">
         <v>1</v>
       </c>
@@ -14521,22 +14528,22 @@
     </row>
     <row r="93" spans="1:18">
       <c r="A93" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>375</v>
+        <v>55</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>24</v>
@@ -14552,10 +14559,10 @@
         <v>27</v>
       </c>
       <c r="L93" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="M93" s="2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
@@ -14565,13 +14572,13 @@
     </row>
     <row r="94" spans="1:18">
       <c r="A94" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>21</v>
@@ -14596,12 +14603,12 @@
         <v>27</v>
       </c>
       <c r="L94" s="2">
-        <v>2</v>
-      </c>
-      <c r="M94" s="2">
-        <v>2</v>
-      </c>
-      <c r="N94" s="1"/>
+        <v>485</v>
+      </c>
+      <c r="M94" s="1"/>
+      <c r="N94" s="2">
+        <v>485</v>
+      </c>
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
@@ -14609,13 +14616,13 @@
     </row>
     <row r="95" spans="1:18">
       <c r="A95" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>21</v>
@@ -14640,10 +14647,10 @@
         <v>27</v>
       </c>
       <c r="L95" s="2">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="M95" s="2">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
@@ -14653,19 +14660,19 @@
     </row>
     <row r="96" spans="1:18">
       <c r="A96" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -14684,32 +14691,34 @@
         <v>27</v>
       </c>
       <c r="L96" s="2">
-        <v>711</v>
-      </c>
-      <c r="M96" s="2">
-        <v>711</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M96" s="1"/>
       <c r="N96" s="1"/>
-      <c r="O96" s="1"/>
-      <c r="P96" s="1"/>
+      <c r="O96" s="2">
+        <v>2</v>
+      </c>
+      <c r="P96" s="2">
+        <v>2</v>
+      </c>
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
     </row>
     <row r="97" spans="1:18">
       <c r="A97" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -14728,34 +14737,32 @@
         <v>27</v>
       </c>
       <c r="L97" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="2">
         <v>2</v>
       </c>
-      <c r="P97" s="2">
-        <v>2</v>
-      </c>
+      <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
     <row r="98" spans="1:18">
       <c r="A98" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -14774,32 +14781,32 @@
         <v>27</v>
       </c>
       <c r="L98" s="2">
-        <v>2</v>
-      </c>
-      <c r="M98" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="M98" s="2">
+        <v>1</v>
+      </c>
       <c r="N98" s="1"/>
-      <c r="O98" s="2">
-        <v>2</v>
-      </c>
+      <c r="O98" s="1"/>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
     <row r="99" spans="1:18">
       <c r="A99" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>392</v>
+        <v>294</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -14820,30 +14827,30 @@
       <c r="L99" s="2">
         <v>1</v>
       </c>
-      <c r="M99" s="2">
-        <v>1</v>
-      </c>
+      <c r="M99" s="1"/>
       <c r="N99" s="1"/>
-      <c r="O99" s="1"/>
+      <c r="O99" s="2">
+        <v>1</v>
+      </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
     <row r="100" spans="1:18">
       <c r="A100" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>292</v>
+        <v>400</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -14866,31 +14873,31 @@
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
-      <c r="O100" s="2">
-        <v>1</v>
-      </c>
-      <c r="P100" s="1"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="2">
+        <v>1</v>
+      </c>
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
     <row r="101" spans="1:18">
       <c r="A101" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>397</v>
+        <v>105</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>24</v>
@@ -14908,33 +14915,33 @@
       <c r="L101" s="2">
         <v>1</v>
       </c>
-      <c r="M101" s="1"/>
+      <c r="M101" s="2">
+        <v>1</v>
+      </c>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
-      <c r="P101" s="2">
-        <v>1</v>
-      </c>
+      <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
     <row r="102" spans="1:18">
       <c r="A102" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>85</v>
+        <v>346</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>24</v>
@@ -14952,33 +14959,33 @@
       <c r="L102" s="2">
         <v>1</v>
       </c>
-      <c r="M102" s="2">
-        <v>1</v>
-      </c>
+      <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
-      <c r="P102" s="1"/>
+      <c r="P102" s="2">
+        <v>1</v>
+      </c>
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
     <row r="103" spans="1:18">
       <c r="A103" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>164</v>
+        <v>410</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>24</v>
@@ -14998,31 +15005,31 @@
       </c>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
-      <c r="O103" s="1"/>
-      <c r="P103" s="2">
-        <v>1</v>
-      </c>
+      <c r="O103" s="2">
+        <v>1</v>
+      </c>
+      <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
     <row r="104" spans="1:18">
       <c r="A104" s="1" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>164</v>
+        <v>414</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>24</v>
@@ -15038,10 +15045,10 @@
         <v>27</v>
       </c>
       <c r="L104" s="2">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="M104" s="2">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
@@ -15051,19 +15058,19 @@
     </row>
     <row r="105" spans="1:18">
       <c r="A105" s="1" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>410</v>
+        <v>22</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -15082,32 +15089,32 @@
         <v>27</v>
       </c>
       <c r="L105" s="2">
-        <v>1</v>
-      </c>
-      <c r="M105" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="M105" s="2">
+        <v>2</v>
+      </c>
       <c r="N105" s="1"/>
-      <c r="O105" s="2">
-        <v>1</v>
-      </c>
+      <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
     <row r="106" spans="1:18">
       <c r="A106" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>414</v>
+        <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>23</v>
@@ -15126,26 +15133,26 @@
         <v>27</v>
       </c>
       <c r="L106" s="2">
-        <v>40</v>
-      </c>
-      <c r="M106" s="2">
-        <v>40</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M106" s="1"/>
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
-      <c r="R106" s="1"/>
+      <c r="R106" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="107" spans="1:18">
       <c r="A107" s="1" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>416</v>
+        <v>286</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>21</v>
@@ -15170,10 +15177,10 @@
         <v>27</v>
       </c>
       <c r="L107" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M107" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
@@ -15183,22 +15190,22 @@
     </row>
     <row r="108" spans="1:18">
       <c r="A108" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>22</v>
+        <v>356</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>24</v>
@@ -15216,33 +15223,33 @@
       <c r="L108" s="2">
         <v>1</v>
       </c>
-      <c r="M108" s="1"/>
+      <c r="M108" s="2">
+        <v>1</v>
+      </c>
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
-      <c r="R108" s="2">
-        <v>1</v>
-      </c>
+      <c r="R108" s="1"/>
     </row>
     <row r="109" spans="1:18">
       <c r="A109" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>353</v>
+        <v>55</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>24</v>
@@ -15258,32 +15265,32 @@
         <v>27</v>
       </c>
       <c r="L109" s="2">
-        <v>1</v>
-      </c>
-      <c r="M109" s="2">
-        <v>1</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="M109" s="1"/>
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
-      <c r="P109" s="1"/>
+      <c r="P109" s="2">
+        <v>22</v>
+      </c>
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
     <row r="110" spans="1:18">
       <c r="A110" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>23</v>
@@ -15302,35 +15309,35 @@
         <v>27</v>
       </c>
       <c r="L110" s="2">
-        <v>22</v>
-      </c>
-      <c r="M110" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="M110" s="2">
+        <v>1</v>
+      </c>
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
-      <c r="P110" s="2">
-        <v>22</v>
-      </c>
+      <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
     <row r="111" spans="1:18">
       <c r="A111" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>24</v>
@@ -15348,30 +15355,30 @@
       <c r="L111" s="2">
         <v>1</v>
       </c>
-      <c r="M111" s="2">
-        <v>1</v>
-      </c>
+      <c r="M111" s="1"/>
       <c r="N111" s="1"/>
-      <c r="O111" s="1"/>
+      <c r="O111" s="2">
+        <v>1</v>
+      </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
     <row r="112" spans="1:18">
       <c r="A112" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -15403,22 +15410,22 @@
     </row>
     <row r="113" spans="1:18">
       <c r="A113" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>24</v>
@@ -15447,19 +15454,19 @@
     </row>
     <row r="114" spans="1:18">
       <c r="A114" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>439</v>
+        <v>123</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>23</v>
@@ -15491,22 +15498,22 @@
     </row>
     <row r="115" spans="1:18">
       <c r="A115" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>441</v>
+        <v>134</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>55</v>
+        <v>446</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>24</v>
@@ -15522,32 +15529,34 @@
         <v>27</v>
       </c>
       <c r="L115" s="2">
-        <v>1</v>
-      </c>
-      <c r="M115" s="1"/>
-      <c r="N115" s="1"/>
-      <c r="O115" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M115" s="2">
+        <v>2</v>
+      </c>
+      <c r="N115" s="2">
+        <v>3</v>
+      </c>
+      <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
     </row>
     <row r="116" spans="1:18">
       <c r="A116" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -15566,35 +15575,35 @@
         <v>27</v>
       </c>
       <c r="L116" s="2">
-        <v>1</v>
-      </c>
-      <c r="M116" s="2">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M116" s="1"/>
       <c r="N116" s="1"/>
-      <c r="O116" s="1"/>
+      <c r="O116" s="2">
+        <v>3</v>
+      </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
     </row>
     <row r="117" spans="1:18">
       <c r="A117" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>132</v>
+        <v>451</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>448</v>
+        <v>299</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>343</v>
+        <v>86</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>24</v>
@@ -15610,34 +15619,32 @@
         <v>27</v>
       </c>
       <c r="L117" s="2">
-        <v>5</v>
-      </c>
-      <c r="M117" s="2">
-        <v>2</v>
-      </c>
-      <c r="N117" s="2">
-        <v>3</v>
-      </c>
-      <c r="O117" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="M117" s="1"/>
+      <c r="N117" s="1"/>
+      <c r="O117" s="2">
+        <v>1</v>
+      </c>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
     </row>
     <row r="118" spans="1:18">
       <c r="A118" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>23</v>
@@ -15656,12 +15663,12 @@
         <v>27</v>
       </c>
       <c r="L118" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
       <c r="O118" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
@@ -15669,22 +15676,22 @@
     </row>
     <row r="119" spans="1:18">
       <c r="A119" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>297</v>
+        <v>22</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>24</v>
@@ -15713,22 +15720,22 @@
     </row>
     <row r="120" spans="1:18">
       <c r="A120" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>456</v>
+        <v>134</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>139</v>
+        <v>446</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>24</v>
@@ -15744,32 +15751,34 @@
         <v>27</v>
       </c>
       <c r="L120" s="2">
-        <v>1</v>
-      </c>
-      <c r="M120" s="1"/>
-      <c r="N120" s="1"/>
-      <c r="O120" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M120" s="2">
+        <v>1</v>
+      </c>
+      <c r="N120" s="2">
+        <v>1</v>
+      </c>
+      <c r="O120" s="1"/>
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
     </row>
     <row r="121" spans="1:18">
       <c r="A121" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>23</v>
@@ -15792,31 +15801,31 @@
       </c>
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
-      <c r="O121" s="2">
-        <v>1</v>
-      </c>
-      <c r="P121" s="1"/>
+      <c r="O121" s="1"/>
+      <c r="P121" s="2">
+        <v>1</v>
+      </c>
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
     </row>
     <row r="122" spans="1:18">
       <c r="A122" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>132</v>
+        <v>465</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>448</v>
+        <v>55</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>24</v>
@@ -15832,34 +15841,32 @@
         <v>27</v>
       </c>
       <c r="L122" s="2">
-        <v>2</v>
-      </c>
-      <c r="M122" s="2">
-        <v>1</v>
-      </c>
-      <c r="N122" s="2">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M122" s="1"/>
+      <c r="N122" s="1"/>
       <c r="O122" s="1"/>
-      <c r="P122" s="1"/>
+      <c r="P122" s="2">
+        <v>1</v>
+      </c>
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
     </row>
     <row r="123" spans="1:18">
       <c r="A123" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>464</v>
+        <v>283</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>23</v>
@@ -15880,30 +15887,30 @@
       <c r="L123" s="2">
         <v>1</v>
       </c>
-      <c r="M123" s="1"/>
+      <c r="M123" s="2">
+        <v>1</v>
+      </c>
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
-      <c r="P123" s="2">
-        <v>1</v>
-      </c>
+      <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
     </row>
     <row r="124" spans="1:18">
       <c r="A124" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>23</v>
@@ -15925,23 +15932,23 @@
         <v>1</v>
       </c>
       <c r="M124" s="1"/>
-      <c r="N124" s="1"/>
+      <c r="N124" s="2">
+        <v>1</v>
+      </c>
       <c r="O124" s="1"/>
-      <c r="P124" s="2">
-        <v>1</v>
-      </c>
+      <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
     </row>
     <row r="125" spans="1:18">
       <c r="A125" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>21</v>
@@ -15966,26 +15973,26 @@
         <v>27</v>
       </c>
       <c r="L125" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="M125" s="1"/>
-      <c r="N125" s="2">
-        <v>19</v>
-      </c>
-      <c r="O125" s="1"/>
+      <c r="N125" s="1"/>
+      <c r="O125" s="2">
+        <v>4</v>
+      </c>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
     </row>
     <row r="126" spans="1:18">
       <c r="A126" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>21</v>
@@ -16012,10 +16019,10 @@
       <c r="L126" s="2">
         <v>1</v>
       </c>
-      <c r="M126" s="2">
-        <v>1</v>
-      </c>
-      <c r="N126" s="1"/>
+      <c r="M126" s="1"/>
+      <c r="N126" s="2">
+        <v>1</v>
+      </c>
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
@@ -16023,22 +16030,22 @@
     </row>
     <row r="127" spans="1:18">
       <c r="A127" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>475</v>
+        <v>134</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>39</v>
+        <v>446</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>24</v>
@@ -16054,10 +16061,10 @@
         <v>27</v>
       </c>
       <c r="L127" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M127" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
@@ -16067,19 +16074,19 @@
     </row>
     <row r="128" spans="1:18">
       <c r="A128" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>23</v>
@@ -16098,32 +16105,32 @@
         <v>27</v>
       </c>
       <c r="L128" s="2">
-        <v>4</v>
-      </c>
-      <c r="M128" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="M128" s="2">
+        <v>1</v>
+      </c>
       <c r="N128" s="1"/>
-      <c r="O128" s="2">
-        <v>4</v>
-      </c>
+      <c r="O128" s="1"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
     </row>
     <row r="129" spans="1:18">
       <c r="A129" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>183</v>
+        <v>483</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -16155,22 +16162,22 @@
     </row>
     <row r="130" spans="1:18">
       <c r="A130" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>132</v>
+        <v>486</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>448</v>
+        <v>205</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>24</v>
@@ -16186,10 +16193,10 @@
         <v>27</v>
       </c>
       <c r="L130" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
@@ -16199,19 +16206,19 @@
     </row>
     <row r="131" spans="1:18">
       <c r="A131" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>485</v>
+        <v>238</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -16243,19 +16250,19 @@
     </row>
     <row r="132" spans="1:18">
       <c r="A132" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -16274,10 +16281,10 @@
         <v>27</v>
       </c>
       <c r="L132" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M132" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
@@ -16287,19 +16294,19 @@
     </row>
     <row r="133" spans="1:18">
       <c r="A133" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>239</v>
+        <v>494</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -16331,19 +16338,19 @@
     </row>
     <row r="134" spans="1:18">
       <c r="A134" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -16362,10 +16369,10 @@
         <v>27</v>
       </c>
       <c r="L134" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="M134" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
@@ -16373,50 +16380,6 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
     </row>
-    <row r="135" spans="1:18">
-      <c r="A135" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J135" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L135" s="2">
-        <v>37</v>
-      </c>
-      <c r="M135" s="2">
-        <v>37</v>
-      </c>
-      <c r="N135" s="1"/>
-      <c r="O135" s="1"/>
-      <c r="P135" s="1"/>
-      <c r="Q135" s="1"/>
-      <c r="R135" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
